--- a/DateBase/orders/Nha Thu_2026-4-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-17.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>050801020581076110101085858100</v>
+        <v>050801020581076110101085858105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-4-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,88 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>4</v>
+      </c>
+      <c r="C24" t="str">
+        <v>597_尤加利叶小叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>315_尤加利叶圆叶_Eucalyptus Populus_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F27" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="C28" t="str" xml:space="preserve">
+        <v xml:space="preserve">740_袋鼠爪橙_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>396_米花白_rice flower white_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>490_米花 粉_rice flower pink_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +743,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>050801020581076110101085858105</v>
+        <v>05080102058107611010108585810551015150205550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-4-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-17.xlsx
@@ -685,6 +685,9 @@
       <c r="C31" t="str">
         <v>490_米花 粉_rice flower pink_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -743,7 +746,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05080102058107611010108585810551015150205550</v>
+        <v>05080102058107611010108585810551015150205555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-4-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -689,9 +689,63 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>518_多头鼠尾 紫色_spray veronica purple_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>5</v>
+      </c>
+      <c r="C34" t="str">
+        <v>388_大丽花_dahlia_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>469_络新妇粉_Astilbe pink_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>777_络新妇白_Astilbe white_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -746,7 +800,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05080102058107611010108585810551015150205555</v>
+        <v>050801020581076110101085858105510151502055551055555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-4-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,312 +440,109 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2" t="str">
-        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
       </c>
       <c r="F2" t="str">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" t="str">
-        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
       </c>
       <c r="F3" t="str">
-        <v>80</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="str">
-        <v>643_巧克力秋英_undefined_undefined_1bunch</v>
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
       </c>
       <c r="F4" t="str">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
       </c>
       <c r="F5" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>669_大丽花 红_undefined_undefined_5stems</v>
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F6" t="str">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>2</v>
-      </c>
       <c r="C7" t="str">
-        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F7" t="str">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F8" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="str">
-        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F9" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="str">
-        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
       </c>
       <c r="F10" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="str">
+        <v>7</v>
+      </c>
       <c r="C11" t="str">
-        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="str">
-        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+        <v>602_康乃馨白_white_undefined_20stems</v>
       </c>
       <c r="F12" t="str">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="str">
-        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+        <v>611_康乃馨奶油白_cream white_undefined_20stems</v>
       </c>
       <c r="F13" t="str">
         <v>10</v>
       </c>
     </row>
-    <row r="14">
-      <c r="C14" t="str">
-        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
-      </c>
-      <c r="F14" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3</v>
-      </c>
-      <c r="C15" t="str">
-        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F15" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="str">
-        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F16" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="str">
-        <v>251_暖暖_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F17" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="str">
-        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F18" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>227_多头卡布奇诺_Cappuccino spray_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F19" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="str">
-        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F20" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="str">
-        <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F21" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="str">
-        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F22" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="str">
-        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F23" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>4</v>
-      </c>
-      <c r="C24" t="str">
-        <v>597_尤加利叶小叶_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F24" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="str">
-        <v>315_尤加利叶圆叶_Eucalyptus Populus_undefined_1bunch</v>
-      </c>
-      <c r="F25" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="str">
-        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="str">
-        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
-      </c>
-      <c r="F27" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="C28" t="str" xml:space="preserve">
-        <v xml:space="preserve">740_袋鼠爪橙_Kangaroo Paw
-red /green /orange / yellow_undefined_1bunch</v>
-      </c>
-      <c r="F28" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="C29" t="str" xml:space="preserve">
-        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
-red /green /orange / yellow_undefined_1bunch</v>
-      </c>
-      <c r="F29" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="str">
-        <v>396_米花白_rice flower white_undefined_1bunch</v>
-      </c>
-      <c r="F30" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="str">
-        <v>490_米花 粉_rice flower pink_undefined_1bunch</v>
-      </c>
-      <c r="F31" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="str">
-        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
-      </c>
-      <c r="F32" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="str">
-        <v>518_多头鼠尾 紫色_spray veronica purple_undefined_1bunch</v>
-      </c>
-      <c r="F33" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>5</v>
-      </c>
-      <c r="C34" t="str">
-        <v>388_大丽花_dahlia_undefined_1bunch</v>
-      </c>
-      <c r="F34" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="str">
-        <v>469_络新妇粉_Astilbe pink_undefined_1bunch</v>
-      </c>
-      <c r="F35" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v/>
-      </c>
-      <c r="C36" t="str">
-        <v>777_络新妇白_Astilbe white_undefined_1bunch</v>
-      </c>
-      <c r="F36" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="str">
-        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
-      </c>
-      <c r="F37" t="str">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -800,7 +597,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>050801020581076110101085858105510151502055551055555</v>
+        <v>010151530556101052010</v>
       </c>
     </row>
   </sheetData>
